--- a/jurnal_konsumen.xlsx
+++ b/jurnal_konsumen.xlsx
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Lain-Lain\Kedai Matera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7868A-1CAC-4FBE-8A30-568F30687A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5627A9E-754C-4750-93FB-07DE8F539B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
   <si>
     <t>Tanggal</t>
   </si>
@@ -127,16 +136,25 @@
   </si>
   <si>
     <t>Meja MEJA 020</t>
+  </si>
+  <si>
+    <t>03-09-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -164,7 +182,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,8 +515,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>46268</v>
+      <c r="A2" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -520,8 +538,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>46268</v>
+      <c r="A3" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -543,8 +561,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>46268</v>
+      <c r="A4" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -566,8 +584,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46268</v>
+      <c r="A5" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -589,8 +607,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>46268</v>
+      <c r="A6" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -612,8 +630,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46268</v>
+      <c r="A7" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -635,8 +653,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>46268</v>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -1233,6 +1251,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>